--- a/GroceryApplicationProject/src/test/resources/TestData.xlsx
+++ b/GroceryApplicationProject/src/test/resources/TestData.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\GroceryRepo\GroceryApplicationProject\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE23424D-2F6F-43F5-85B1-45ECFC041969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96A3E88-C624-4F74-AB92-1732D08FE7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
+    <sheet name="AdminUsersPage" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t xml:space="preserve">admin </t>
   </si>
@@ -34,6 +35,12 @@
   </si>
   <si>
     <t>sr1234</t>
+  </si>
+  <si>
+    <t>Sruthi Sankar</t>
+  </si>
+  <si>
+    <t>Sruthi</t>
   </si>
 </sst>
 </file>
@@ -414,4 +421,26 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9045F431-9E26-4E5D-A7D2-66681AC73D59}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/GroceryApplicationProject/src/test/resources/TestData.xlsx
+++ b/GroceryApplicationProject/src/test/resources/TestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\GroceryRepo\GroceryApplicationProject\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96A3E88-C624-4F74-AB92-1732D08FE7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFBEBC54-DA26-4B4B-85BD-21FD6D78A855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t xml:space="preserve">admin </t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>Sruthi</t>
+  </si>
+  <si>
+    <t>dummy123</t>
+  </si>
+  <si>
+    <t>dummy</t>
   </si>
 </sst>
 </file>
@@ -377,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.54296875" style="1" customWidth="1"/>
@@ -415,6 +421,14 @@
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
